--- a/DCTBFSSeeding.xlsx
+++ b/DCTBFSSeeding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d110c23d71eaefdd/Documents/GitHub/DCTBFightingSimulator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{23AC14D1-B86B-4059-B0E9-4035EB929E0E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{E32E5AFB-01F1-451F-9AF9-7276D06E6DFE}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{23AC14D1-B86B-4059-B0E9-4035EB929E0E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{5D866D93-C4F2-4E88-B85E-A768E79648BF}"/>
   <bookViews>
-    <workbookView xWindow="2865" yWindow="3915" windowWidth="21600" windowHeight="11385" xr2:uid="{E8889201-C7C1-48DA-B9B8-2B3B605CA93E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E8889201-C7C1-48DA-B9B8-2B3B605CA93E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1134,7 +1134,9 @@
       <c r="I22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="11"/>
+      <c r="J22" s="11">
+        <v>1</v>
+      </c>
       <c r="K22" s="10" t="s">
         <v>32</v>
       </c>
@@ -1158,7 +1160,9 @@
       <c r="I23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="11"/>
+      <c r="J23" s="11">
+        <v>1</v>
+      </c>
       <c r="K23" s="10" t="s">
         <v>32</v>
       </c>
@@ -1182,7 +1186,9 @@
       <c r="I24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="11"/>
+      <c r="J24" s="11">
+        <v>1</v>
+      </c>
       <c r="K24" s="10" t="s">
         <v>32</v>
       </c>
@@ -1206,7 +1212,9 @@
       <c r="I25" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J25" s="11"/>
+      <c r="J25" s="11">
+        <v>1</v>
+      </c>
       <c r="K25" s="10" t="s">
         <v>32</v>
       </c>
